--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,101 +572,101 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H2" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I2" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
         <v>20260528</v>
       </c>
-      <c r="B3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="B4" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" t="n">
         <v>10.07</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" t="n">
         <v>4.73</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>930955</v>
@@ -735,7 +735,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.68</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>930955</v>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>930955</v>
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>930955</v>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>930955</v>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>930955</v>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>930955</v>
@@ -1052,21 +1052,21 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>930955</v>
@@ -1092,13 +1092,13 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>5.15</v>
@@ -1106,7 +1106,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1132,21 +1132,21 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1346,7 +1346,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1381,6 +1381,46 @@
         <v>4.5</v>
       </c>
       <c r="J22" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J23" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -575,18 +575,18 @@
         <v>8.83</v>
       </c>
       <c r="H2" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I2" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J2" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,101 +612,101 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H3" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I3" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J3" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B4" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>20260528</v>
       </c>
-      <c r="B4" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="B5" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>10.07</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>4.73</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>930955</v>
@@ -732,21 +732,21 @@
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>930955</v>
@@ -775,7 +775,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>4.68</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>930955</v>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>930955</v>
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>930955</v>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>930955</v>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>930955</v>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>930955</v>
@@ -1052,21 +1052,21 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>930955</v>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>5.15</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1421,6 +1421,46 @@
         <v>4.5</v>
       </c>
       <c r="J23" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H2" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I2" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J2" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -615,18 +615,18 @@
         <v>8.83</v>
       </c>
       <c r="H3" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I3" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J3" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,101 +652,101 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H4" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I4" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J4" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B5" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>20260528</v>
       </c>
-      <c r="B5" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="B6" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>10.07</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>4.73</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>930955</v>
@@ -815,7 +815,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>4.68</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>930955</v>
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>930955</v>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>930955</v>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>930955</v>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>930955</v>
@@ -1052,21 +1052,21 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>930955</v>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1132,21 +1132,21 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>5.15</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1461,6 +1461,46 @@
         <v>4.5</v>
       </c>
       <c r="J24" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J25" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260605</v>
+        <v>20260608</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.74</v>
+        <v>8.82</v>
       </c>
       <c r="H2" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J2" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260604</v>
+        <v>20260605</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="H3" t="n">
         <v>10.18</v>
       </c>
       <c r="I3" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="J3" t="n">
         <v>5.22</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260603</v>
+        <v>20260604</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="H4" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="I4" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J4" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B5" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H5" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I5" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B6" t="n">
         <v>930955</v>
@@ -735,18 +735,18 @@
         <v>8.83</v>
       </c>
       <c r="H6" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I6" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J6" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B7" t="n">
         <v>930955</v>
@@ -772,101 +772,101 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H7" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I7" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J7" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B8" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
         <v>20260528</v>
       </c>
-      <c r="B8" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="B9" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" t="n">
         <v>10.07</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>4.73</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>930955</v>
@@ -935,7 +935,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>4.68</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>930955</v>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>930955</v>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>930955</v>
@@ -1052,21 +1052,21 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>930955</v>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1132,21 +1132,21 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,13 +1292,13 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>5.15</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>930955</v>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>930955</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>930955</v>
@@ -1581,6 +1581,46 @@
         <v>4.5</v>
       </c>
       <c r="J27" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J28" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260610</v>
+        <v>20260611</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>10.08</v>
+        <v>10.01</v>
       </c>
       <c r="I2" t="n">
         <v>5.03</v>
       </c>
       <c r="J2" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260609</v>
+        <v>20260610</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,21 +612,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="J3" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260608</v>
+        <v>20260609</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260605</v>
+        <v>20260608</v>
       </c>
       <c r="B5" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.74</v>
+        <v>8.82</v>
       </c>
       <c r="H5" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J5" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260604</v>
+        <v>20260605</v>
       </c>
       <c r="B6" t="n">
         <v>930955</v>
@@ -732,13 +732,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="H6" t="n">
         <v>10.18</v>
       </c>
       <c r="I6" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="J6" t="n">
         <v>5.22</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260603</v>
+        <v>20260604</v>
       </c>
       <c r="B7" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="H7" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="I7" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J7" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B8" t="n">
         <v>930955</v>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H8" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I8" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J8" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B9" t="n">
         <v>930955</v>
@@ -855,18 +855,18 @@
         <v>8.83</v>
       </c>
       <c r="H9" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I9" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J9" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B10" t="n">
         <v>930955</v>
@@ -892,101 +892,101 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H10" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I10" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J10" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B11" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>20260528</v>
       </c>
-      <c r="B11" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="B12" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>10.07</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" t="n">
         <v>4.73</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>930955</v>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>930955</v>
@@ -1055,7 +1055,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>4.68</v>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>930955</v>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I15" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1132,21 +1132,21 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1412,13 +1412,13 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>5.15</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>930955</v>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>930955</v>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>930955</v>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>930955</v>
@@ -1612,21 +1612,21 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>930955</v>
@@ -1666,7 +1666,7 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>930955</v>
@@ -1701,6 +1701,46 @@
         <v>4.5</v>
       </c>
       <c r="J30" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J31" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260612</v>
+        <v>20260615</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.949999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="H2" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="I2" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260611</v>
+        <v>20260612</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,21 +612,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>10.01</v>
+        <v>10.11</v>
       </c>
       <c r="I3" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260610</v>
+        <v>20260611</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>10.08</v>
+        <v>10.01</v>
       </c>
       <c r="I4" t="n">
         <v>5.03</v>
       </c>
       <c r="J4" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260609</v>
+        <v>20260610</v>
       </c>
       <c r="B5" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="J5" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260608</v>
+        <v>20260609</v>
       </c>
       <c r="B6" t="n">
         <v>930955</v>
@@ -732,21 +732,21 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="I6" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="J6" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260605</v>
+        <v>20260608</v>
       </c>
       <c r="B7" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.74</v>
+        <v>8.82</v>
       </c>
       <c r="H7" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="I7" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J7" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260604</v>
+        <v>20260605</v>
       </c>
       <c r="B8" t="n">
         <v>930955</v>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="H8" t="n">
         <v>10.18</v>
       </c>
       <c r="I8" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="J8" t="n">
         <v>5.22</v>
@@ -826,7 +826,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260603</v>
+        <v>20260604</v>
       </c>
       <c r="B9" t="n">
         <v>930955</v>
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="H9" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="I9" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J9" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B10" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H10" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I10" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J10" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B11" t="n">
         <v>930955</v>
@@ -935,18 +935,18 @@
         <v>8.83</v>
       </c>
       <c r="H11" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I11" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J11" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B12" t="n">
         <v>930955</v>
@@ -972,101 +972,101 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H12" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I12" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J12" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B13" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
         <v>20260528</v>
       </c>
-      <c r="B13" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="B14" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" t="n">
         <v>10.07</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" t="n">
         <v>4.73</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>930955</v>
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1135,7 +1135,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>4.68</v>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>930955</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>5.15</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>930955</v>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>930955</v>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>930955</v>
@@ -1612,21 +1612,21 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>930955</v>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>930955</v>
@@ -1692,21 +1692,21 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>930955</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>930955</v>
@@ -1781,6 +1781,46 @@
         <v>4.5</v>
       </c>
       <c r="J32" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J33" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260615</v>
+        <v>20260616</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.68</v>
+        <v>8.56</v>
       </c>
       <c r="H2" t="n">
-        <v>10.3</v>
+        <v>10.14</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
       <c r="J2" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260612</v>
+        <v>20260615</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,21 +612,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.949999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="H3" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260611</v>
+        <v>20260612</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>10.01</v>
+        <v>10.11</v>
       </c>
       <c r="I4" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="J4" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260610</v>
+        <v>20260611</v>
       </c>
       <c r="B5" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>10.08</v>
+        <v>10.01</v>
       </c>
       <c r="I5" t="n">
         <v>5.03</v>
       </c>
       <c r="J5" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260609</v>
+        <v>20260610</v>
       </c>
       <c r="B6" t="n">
         <v>930955</v>
@@ -732,21 +732,21 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="I6" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="J6" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260608</v>
+        <v>20260609</v>
       </c>
       <c r="B7" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="I7" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="J7" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260605</v>
+        <v>20260608</v>
       </c>
       <c r="B8" t="n">
         <v>930955</v>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8.74</v>
+        <v>8.82</v>
       </c>
       <c r="H8" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="I8" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J8" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260604</v>
+        <v>20260605</v>
       </c>
       <c r="B9" t="n">
         <v>930955</v>
@@ -852,13 +852,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="H9" t="n">
         <v>10.18</v>
       </c>
       <c r="I9" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="J9" t="n">
         <v>5.22</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260603</v>
+        <v>20260604</v>
       </c>
       <c r="B10" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="H10" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="I10" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J10" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B11" t="n">
         <v>930955</v>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H11" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I11" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J11" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B12" t="n">
         <v>930955</v>
@@ -975,18 +975,18 @@
         <v>8.83</v>
       </c>
       <c r="H12" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I12" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J12" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B13" t="n">
         <v>930955</v>
@@ -1012,101 +1012,101 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H13" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I13" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J13" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B14" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H14" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I14" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
         <v>20260528</v>
       </c>
-      <c r="B14" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="B15" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>10.07</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" t="n">
         <v>4.73</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H15" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>930955</v>
@@ -1132,21 +1132,21 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1175,7 +1175,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>4.68</v>
@@ -1186,7 +1186,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>930955</v>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>930955</v>
@@ -1532,13 +1532,13 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>5.15</v>
@@ -1546,7 +1546,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>930955</v>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>930955</v>
@@ -1612,21 +1612,21 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>930955</v>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>930955</v>
@@ -1692,21 +1692,21 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>930955</v>
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>930955</v>
@@ -1786,7 +1786,7 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>930955</v>
@@ -1821,6 +1821,46 @@
         <v>4.5</v>
       </c>
       <c r="J33" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J34" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260616</v>
+        <v>20260617</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.56</v>
+        <v>8.49</v>
       </c>
       <c r="H2" t="n">
-        <v>10.14</v>
+        <v>10.06</v>
       </c>
       <c r="I2" t="n">
-        <v>4.97</v>
+        <v>5.01</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260615</v>
+        <v>20260616</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,21 +612,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.68</v>
+        <v>8.56</v>
       </c>
       <c r="H3" t="n">
-        <v>10.3</v>
+        <v>10.14</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
       <c r="J3" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260612</v>
+        <v>20260615</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.949999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="H4" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260611</v>
+        <v>20260612</v>
       </c>
       <c r="B5" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>10.01</v>
+        <v>10.11</v>
       </c>
       <c r="I5" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260610</v>
+        <v>20260611</v>
       </c>
       <c r="B6" t="n">
         <v>930955</v>
@@ -732,21 +732,21 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>10.08</v>
+        <v>10.01</v>
       </c>
       <c r="I6" t="n">
         <v>5.03</v>
       </c>
       <c r="J6" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260609</v>
+        <v>20260610</v>
       </c>
       <c r="B7" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="I7" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="J7" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260608</v>
+        <v>20260609</v>
       </c>
       <c r="B8" t="n">
         <v>930955</v>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="I8" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260605</v>
+        <v>20260608</v>
       </c>
       <c r="B9" t="n">
         <v>930955</v>
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8.74</v>
+        <v>8.82</v>
       </c>
       <c r="H9" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J9" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260604</v>
+        <v>20260605</v>
       </c>
       <c r="B10" t="n">
         <v>930955</v>
@@ -892,13 +892,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="H10" t="n">
         <v>10.18</v>
       </c>
       <c r="I10" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="J10" t="n">
         <v>5.22</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260603</v>
+        <v>20260604</v>
       </c>
       <c r="B11" t="n">
         <v>930955</v>
@@ -932,21 +932,21 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="H11" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="I11" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J11" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B12" t="n">
         <v>930955</v>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H12" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I12" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J12" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B13" t="n">
         <v>930955</v>
@@ -1015,18 +1015,18 @@
         <v>8.83</v>
       </c>
       <c r="H13" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I13" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J13" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B14" t="n">
         <v>930955</v>
@@ -1052,101 +1052,101 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H14" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I14" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J14" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B15" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I15" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>20260528</v>
       </c>
-      <c r="B15" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="B16" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>10.07</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>4.73</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B17" s="3" t="n">
         <v>930955</v>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1215,7 +1215,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I18" s="3" t="n">
         <v>4.68</v>
@@ -1226,7 +1226,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>930955</v>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>930955</v>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>930955</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.15</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>930955</v>
@@ -1612,21 +1612,21 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>930955</v>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>930955</v>
@@ -1692,21 +1692,21 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>930955</v>
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>930955</v>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>930955</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>930955</v>
@@ -1861,6 +1861,46 @@
         <v>4.5</v>
       </c>
       <c r="J34" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J35" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>

--- a/930955indicator.xlsx
+++ b/930955indicator.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
     <col width="8.83203125" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260617</v>
+        <v>20260618</v>
       </c>
       <c r="B2" t="n">
         <v>930955</v>
@@ -572,21 +572,21 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8.49</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>10.06</v>
+        <v>9.85</v>
       </c>
       <c r="I2" t="n">
-        <v>5.01</v>
+        <v>5.13</v>
       </c>
       <c r="J2" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260616</v>
+        <v>20260617</v>
       </c>
       <c r="B3" t="n">
         <v>930955</v>
@@ -612,21 +612,21 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8.56</v>
+        <v>8.49</v>
       </c>
       <c r="H3" t="n">
-        <v>10.14</v>
+        <v>10.06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.97</v>
+        <v>5.01</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260615</v>
+        <v>20260616</v>
       </c>
       <c r="B4" t="n">
         <v>930955</v>
@@ -652,21 +652,21 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8.68</v>
+        <v>8.56</v>
       </c>
       <c r="H4" t="n">
-        <v>10.3</v>
+        <v>10.14</v>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.97</v>
       </c>
       <c r="J4" t="n">
-        <v>5.03</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260612</v>
+        <v>20260615</v>
       </c>
       <c r="B5" t="n">
         <v>930955</v>
@@ -692,21 +692,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.68</v>
       </c>
       <c r="H5" t="n">
-        <v>10.11</v>
+        <v>10.3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>5.25</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260611</v>
+        <v>20260612</v>
       </c>
       <c r="B6" t="n">
         <v>930955</v>
@@ -732,21 +732,21 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>8.869999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>10.01</v>
+        <v>10.11</v>
       </c>
       <c r="I6" t="n">
-        <v>5.03</v>
+        <v>4.98</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260610</v>
+        <v>20260611</v>
       </c>
       <c r="B7" t="n">
         <v>930955</v>
@@ -772,21 +772,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>10.08</v>
+        <v>10.01</v>
       </c>
       <c r="I7" t="n">
         <v>5.03</v>
       </c>
       <c r="J7" t="n">
-        <v>5.26</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260609</v>
+        <v>20260610</v>
       </c>
       <c r="B8" t="n">
         <v>930955</v>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>10.07</v>
+        <v>10.08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.07</v>
+        <v>5.03</v>
       </c>
       <c r="J8" t="n">
-        <v>5.27</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260608</v>
+        <v>20260609</v>
       </c>
       <c r="B9" t="n">
         <v>930955</v>
@@ -852,21 +852,21 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="I9" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="J9" t="n">
-        <v>5.26</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260605</v>
+        <v>20260608</v>
       </c>
       <c r="B10" t="n">
         <v>930955</v>
@@ -892,21 +892,21 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8.74</v>
+        <v>8.82</v>
       </c>
       <c r="H10" t="n">
-        <v>10.18</v>
+        <v>10.1</v>
       </c>
       <c r="I10" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J10" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260604</v>
+        <v>20260605</v>
       </c>
       <c r="B11" t="n">
         <v>930955</v>
@@ -932,13 +932,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="H11" t="n">
         <v>10.18</v>
       </c>
       <c r="I11" t="n">
-        <v>5.14</v>
+        <v>5.11</v>
       </c>
       <c r="J11" t="n">
         <v>5.22</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260603</v>
+        <v>20260604</v>
       </c>
       <c r="B12" t="n">
         <v>930955</v>
@@ -972,21 +972,21 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>8.77</v>
+        <v>8.68</v>
       </c>
       <c r="H12" t="n">
-        <v>10.29</v>
+        <v>10.18</v>
       </c>
       <c r="I12" t="n">
-        <v>5.09</v>
+        <v>5.14</v>
       </c>
       <c r="J12" t="n">
-        <v>5.16</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260602</v>
+        <v>20260603</v>
       </c>
       <c r="B13" t="n">
         <v>930955</v>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8.83</v>
+        <v>8.77</v>
       </c>
       <c r="H13" t="n">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="I13" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="J13" t="n">
-        <v>5.12</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260601</v>
+        <v>20260602</v>
       </c>
       <c r="B14" t="n">
         <v>930955</v>
@@ -1055,18 +1055,18 @@
         <v>8.83</v>
       </c>
       <c r="H14" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="I14" t="n">
-        <v>5.06</v>
+        <v>5.05</v>
       </c>
       <c r="J14" t="n">
-        <v>5.09</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20260529</v>
+        <v>20260601</v>
       </c>
       <c r="B15" t="n">
         <v>930955</v>
@@ -1092,101 +1092,101 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>8.73</v>
+        <v>8.83</v>
       </c>
       <c r="H15" t="n">
-        <v>10.26</v>
+        <v>10.43</v>
       </c>
       <c r="I15" t="n">
-        <v>5.11</v>
+        <v>5.06</v>
       </c>
       <c r="J15" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>20260529</v>
+      </c>
+      <c r="B16" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="H16" t="n">
+        <v>10.26</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>20260528</v>
       </c>
-      <c r="B16" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="B17" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
         <v>8.550000000000001</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" t="n">
         <v>10.07</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" t="n">
         <v>4.73</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>5.33</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>20260527</v>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>930955</v>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>中证红利低波动100指数</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>红利低波100</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>CSI Dividend Low Volatility 100 Index</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Dividend Low Volatility100</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H17" s="3" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>5.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>20260526</v>
+        <v>20260527</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>930955</v>
@@ -1212,21 +1212,21 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.19</v>
+        <v>10.16</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4.68</v>
+        <v>4.69</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>20260525</v>
+        <v>20260526</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>930955</v>
@@ -1255,7 +1255,7 @@
         <v>8.640000000000001</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>10.18</v>
+        <v>10.19</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>4.68</v>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>20260522</v>
+        <v>20260525</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>930955</v>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>8.65</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>10.15</v>
+        <v>10.18</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>4.68</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>5.29</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>20260521</v>
+        <v>20260522</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>930955</v>
@@ -1332,21 +1332,21 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>8.68</v>
+        <v>8.65</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>10.2</v>
+        <v>10.15</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>5.27</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>20260520</v>
+        <v>20260521</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>930955</v>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>10.27</v>
+        <v>10.2</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>4.66</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>5.23</v>
+        <v>5.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>20260519</v>
+        <v>20260520</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>930955</v>
@@ -1412,21 +1412,21 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>10.34</v>
+        <v>10.27</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>4.6</v>
+        <v>4.66</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>20260518</v>
+        <v>20260519</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>930955</v>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.75</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>10.25</v>
+        <v>10.34</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>5.24</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>20260515</v>
+        <v>20260518</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>930955</v>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>10.31</v>
+        <v>10.25</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>4.6</v>
+        <v>4.63</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>5.21</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>20260514</v>
+        <v>20260515</v>
       </c>
       <c r="B26" s="3" t="n">
         <v>930955</v>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>10.36</v>
+        <v>10.31</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.58</v>
+        <v>4.6</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>5.18</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>20260513</v>
+        <v>20260514</v>
       </c>
       <c r="B27" s="3" t="n">
         <v>930955</v>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>8.82</v>
+        <v>8.84</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.15</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>20260512</v>
+        <v>20260513</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>930955</v>
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.55</v>
+        <v>4.59</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>5.15</v>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>20260511</v>
+        <v>20260512</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>930955</v>
@@ -1652,21 +1652,21 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>10.45</v>
+        <v>10.43</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>4.55</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>20260508</v>
+        <v>20260511</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>930955</v>
@@ -1692,21 +1692,21 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>10.41</v>
+        <v>10.45</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>4.54</v>
+        <v>4.55</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>20260507</v>
+        <v>20260508</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>930955</v>
@@ -1732,21 +1732,21 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>10.4</v>
+        <v>10.41</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>20260506</v>
+        <v>20260507</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>930955</v>
@@ -1772,21 +1772,21 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>8.94</v>
+        <v>8.9</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>10.43</v>
+        <v>10.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>5.15</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>20260505</v>
+        <v>20260506</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>930955</v>
@@ -1812,21 +1812,21 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>8.779999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>9.6</v>
+        <v>10.43</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>5.14</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>20260504</v>
+        <v>20260505</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>930955</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>20260430</v>
+        <v>20260504</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>930955</v>
@@ -1901,6 +1901,46 @@
         <v>4.5</v>
       </c>
       <c r="J35" s="3" t="n">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="n">
+        <v>20260430</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>930955</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>CSI Dividend Low Volatility 100 Index</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Dividend Low Volatility100</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J36" s="3" t="n">
         <v>5.14</v>
       </c>
     </row>
